--- a/public/samples/WattToAmpere.xlsx
+++ b/public/samples/WattToAmpere.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\programing\backend testing\dev sync for wattwizart\public\samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M\Downloads\ezzat\WattWizards\backend\public\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6434A5BC-10F2-441F-A477-2C96C813A6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A65570C-B37F-4E2F-A04E-723202B6C0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,19 +28,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>powerFactor</t>
-  </si>
-  <si>
     <t>Voltage</t>
   </si>
   <si>
-    <t>phases</t>
+    <t>Watt</t>
   </si>
   <si>
-    <t>CurrentType</t>
+    <t>Power factor</t>
   </si>
   <si>
-    <t>Watt</t>
+    <t>Phases</t>
+  </si>
+  <si>
+    <t>Current type</t>
   </si>
 </sst>
 </file>
@@ -388,19 +388,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
